--- a/daily_output/Shopee_upload_TH_2026-09-30.xlsx
+++ b/daily_output/Shopee_upload_TH_2026-09-30.xlsx
@@ -13238,7 +13238,7 @@
     <t xml:space="preserve">B0DZBYTRT4</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/51oSdv6NqYL._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0DZBYTRT4_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/41OWrXf9REL._AC_SL1000_.jpg</t>
@@ -13278,7 +13278,7 @@
     <t xml:space="preserve">B0GM5T4521</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/51MFOgwDPrL._AC_SL1280_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0GM5T4521_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">On</t>
@@ -13300,7 +13300,7 @@
     <t xml:space="preserve">B0F6CZQLM2</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61QlbMMWAXL._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0F6CZQLM2_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/514-PG2Wu5L.jpg</t>
